--- a/11_compliance-mapping-for-ai-systems-gdpr-cpra/exercises/solution/data_retention_solution.xlsx
+++ b/11_compliance-mapping-for-ai-systems-gdpr-cpra/exercises/solution/data_retention_solution.xlsx
@@ -1976,7 +1976,7 @@
       <c r="B11" s="11" t="inlineStr">
         <is>
           <t>"Supervisory Notification (if needed)"
-Reasoning: Some jurisdictions require DPA notification for certain deletion types; 30-day window per GDPR</t>
+Reasoning: Some jurisdictions require DPA notification for certain deletion types; one-month default per Art. 12(3) (extendable by two further months for complex / numerous requests)</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>DPA escalation per Art. 33-34</t>
+          <t>DPA escalation per Art. 12(3) (extended response window) and Art. 77 (supervisory authority complaint route)</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>GDPR Art. 5(f) - Integrity</t>
+          <t>GDPR Art. 5(1)(f) - Integrity</t>
         </is>
       </c>
     </row>

--- a/11_compliance-mapping-for-ai-systems-gdpr-cpra/exercises/solution/data_retention_solution.xlsx
+++ b/11_compliance-mapping-for-ai-systems-gdpr-cpra/exercises/solution/data_retention_solution.xlsx
@@ -588,7 +588,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>3. Document 8 retraining triggers mapping deleted data to affected models</t>
+          <t>3. Document the 5 retraining triggers mapping deleted data to affected models</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr"/>

--- a/11_compliance-mapping-for-ai-systems-gdpr-cpra/exercises/solution/data_retention_solution.xlsx
+++ b/11_compliance-mapping-for-ai-systems-gdpr-cpra/exercises/solution/data_retention_solution.xlsx
@@ -1040,8 +1040,8 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>7 years
-Reasoning: HIPAA/GDPR require 6-7 year audit retention</t>
+          <t>"7 years"
+Reasoning: HIPAA's 6-year rule covers Security-Rule documentation; GDPR fixes no audit-log retention period. 7 years is an internal standard layered on top.</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">

--- a/11_compliance-mapping-for-ai-systems-gdpr-cpra/exercises/solution/data_retention_solution.xlsx
+++ b/11_compliance-mapping-for-ai-systems-gdpr-cpra/exercises/solution/data_retention_solution.xlsx
@@ -1229,7 +1229,7 @@
       <c r="D9" s="11" t="inlineStr">
         <is>
           <t>"Art. 6(1)(c) - Legal Obligation"
-Reasoning: Legal obligation for audit trail; 7 years is standard compliance retention; WORM ensures immutability</t>
+Reasoning: Legal obligation to maintain an audit trail; the 7-year period is an internal standard, not a statutory retention term; WORM ensures immutability</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>Must retain full 7 years by regulation</t>
+          <t>Audit-trail obligation prevents early deletion; the 7-year period is an internal standard, not fixed by regulation</t>
         </is>
       </c>
       <c r="K9" s="11" t="inlineStr">
